--- a/tables/ov_1_clean_test_anomalous_reconstruction_examples/row_1031_reconstruction.xlsx
+++ b/tables/ov_1_clean_test_anomalous_reconstruction_examples/row_1031_reconstruction.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconstruction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekonstruktion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reconstruction'!$A$4:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rekonstruktion'!$A$4:$D$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,36 +480,36 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clean Validation Reconstruction Example - Row 1031</t>
+          <t>Rekonstruktionsbeispiel - Zeile 1031</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Resource: ov_1 | Row Loss (MSE, scaled): 1.076918 | Threshold: 0.800319</t>
+          <t>Ressource: ov_1 | Zeilenfehler (MSE, skaliert): 1.076918 | Schwelle: 0.800319</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sensor Name</t>
+          <t>Sensorname</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Eingabe</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Reconstruction</t>
+          <t>Rekonstruktion</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Loss (MSE)</t>
+          <t>Fehler (MSE)</t>
         </is>
       </c>
     </row>
